--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/11,08,26 Останкино СЫРЫ/дв 11,08,26 днрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/11,08,26 Останкино СЫРЫ/дв 11,08,26 днрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\11,08,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5A84A0-FB45-4280-ADC6-069E3931D9E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792DE6E-2B75-4C75-B849-10AA0B52E9CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -161,13 +161,7 @@
     <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
   </si>
   <si>
-    <t>30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
-  </si>
-  <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
-  </si>
-  <si>
-    <t>30,07,26 - нет на заводе / 34шт в уценку (28,07,26)</t>
   </si>
   <si>
     <t>4931  Сыр полутвердый "Купеческий" с ароматом топленого молока, с м.д.ж. 50% ОСТАНКИНО</t>
@@ -310,6 +304,12 @@
   <si>
     <t>17,08,сети</t>
   </si>
+  <si>
+    <t>13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
+  </si>
+  <si>
+    <t>13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 34шт в уценку (28,07,26)</t>
+  </si>
 </sst>
 </file>
 
@@ -356,7 +356,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +382,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,7 +427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -438,6 +444,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -928,19 +936,19 @@
         <v>16</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>17</v>
@@ -1026,14 +1034,14 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="T4" s="1"/>
       <c r="U4" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -1138,7 +1146,7 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>996</v>
+        <v>948</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" ref="T5:U5" si="1">SUM(T6:T498)</f>
@@ -1648,7 +1656,7 @@
         <v>6.2723999999999993</v>
       </c>
       <c r="AI9" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ9" s="1">
         <f t="shared" si="8"/>
@@ -1714,9 +1722,8 @@
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="S10" s="5">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>24</v>
+      <c r="S10" s="16">
+        <v>0</v>
       </c>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -1759,8 +1766,8 @@
       <c r="AH10" s="1">
         <v>4.2</v>
       </c>
-      <c r="AI10" s="1" t="s">
-        <v>42</v>
+      <c r="AI10" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="AJ10" s="1">
         <f t="shared" si="8"/>
@@ -1786,7 +1793,7 @@
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>35</v>
@@ -1826,9 +1833,8 @@
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="S11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>24</v>
+      <c r="S11" s="16">
+        <v>0</v>
       </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
@@ -1871,8 +1877,8 @@
       <c r="AH11" s="1">
         <v>3.6</v>
       </c>
-      <c r="AI11" s="1" t="s">
-        <v>44</v>
+      <c r="AI11" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="AJ11" s="1">
         <f t="shared" si="8"/>
@@ -1898,7 +1904,7 @@
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>40</v>
@@ -1983,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ12" s="1">
         <f t="shared" si="8"/>
@@ -2009,7 +2015,7 @@
     </row>
     <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>35</v>
@@ -2090,7 +2096,7 @@
         <v>0.4</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ13" s="1">
         <f t="shared" si="8"/>
@@ -2116,7 +2122,7 @@
     </row>
     <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>35</v>
@@ -2203,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="AI14" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ14" s="1">
         <f t="shared" si="8"/>
@@ -2229,7 +2235,7 @@
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -2316,7 +2322,7 @@
         <v>4</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" si="8"/>
@@ -2342,7 +2348,7 @@
     </row>
     <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>35</v>
@@ -2429,7 +2435,7 @@
         <v>21.4</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" si="8"/>
@@ -2455,7 +2461,7 @@
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>35</v>
@@ -2544,7 +2550,7 @@
         <v>3.6</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ17" s="1">
         <f t="shared" si="8"/>
@@ -2570,7 +2576,7 @@
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>35</v>
@@ -2689,7 +2695,7 @@
     </row>
     <row r="19" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>35</v>
@@ -2808,7 +2814,7 @@
     </row>
     <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>35</v>
@@ -2927,7 +2933,7 @@
     </row>
     <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>35</v>
@@ -3046,7 +3052,7 @@
     </row>
     <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>35</v>
@@ -3129,7 +3135,7 @@
         <v>0.8</v>
       </c>
       <c r="AI22" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ22" s="1">
         <f t="shared" si="8"/>
@@ -3155,7 +3161,7 @@
     </row>
     <row r="23" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>35</v>
@@ -3264,7 +3270,7 @@
     </row>
     <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>35</v>
@@ -3381,7 +3387,7 @@
     </row>
     <row r="25" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
@@ -3494,7 +3500,7 @@
     </row>
     <row r="26" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>35</v>
@@ -3613,7 +3619,7 @@
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>35</v>
@@ -3732,7 +3738,7 @@
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>35</v>
@@ -3819,7 +3825,7 @@
         <v>15.8</v>
       </c>
       <c r="AI28" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AJ28" s="1">
         <f t="shared" si="8"/>
@@ -3845,7 +3851,7 @@
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>35</v>
@@ -3932,7 +3938,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="AI29" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AJ29" s="1">
         <f t="shared" si="8"/>
@@ -3958,7 +3964,7 @@
     </row>
     <row r="30" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>35</v>
@@ -4045,7 +4051,7 @@
         <v>11.2</v>
       </c>
       <c r="AI30" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ30" s="1">
         <f t="shared" si="8"/>
@@ -4071,7 +4077,7 @@
     </row>
     <row r="31" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>35</v>
@@ -4158,7 +4164,7 @@
         <v>4</v>
       </c>
       <c r="AI31" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ31" s="1">
         <f t="shared" si="8"/>
@@ -4184,7 +4190,7 @@
     </row>
     <row r="32" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>35</v>
@@ -4271,7 +4277,7 @@
         <v>69.8</v>
       </c>
       <c r="AI32" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ32" s="1">
         <f t="shared" si="8"/>
@@ -4297,7 +4303,7 @@
     </row>
     <row r="33" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>35</v>
@@ -4350,7 +4356,7 @@
         <v>200</v>
       </c>
       <c r="V33" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="W33" s="1">
         <f t="shared" si="6"/>
@@ -4391,7 +4397,7 @@
         <v>18.2</v>
       </c>
       <c r="AI33" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ33" s="1">
         <f>G33*T33</f>
@@ -4417,7 +4423,7 @@
     </row>
     <row r="34" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -4536,7 +4542,7 @@
     </row>
     <row r="35" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
@@ -4649,7 +4655,7 @@
     </row>
     <row r="36" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>40</v>
@@ -4734,7 +4740,7 @@
         <v>8.0055999999999994</v>
       </c>
       <c r="AI36" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ36" s="1">
         <f t="shared" si="8"/>
@@ -4760,7 +4766,7 @@
     </row>
     <row r="37" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>40</v>
@@ -4847,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ37" s="1">
         <f t="shared" si="8"/>
@@ -4873,7 +4879,7 @@
     </row>
     <row r="38" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>40</v>
@@ -4984,7 +4990,7 @@
     </row>
     <row r="39" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
@@ -5065,7 +5071,7 @@
         <v>3.2023999999999999</v>
       </c>
       <c r="AI39" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ39" s="1">
         <f t="shared" si="8"/>
@@ -5091,7 +5097,7 @@
     </row>
     <row r="40" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>35</v>
@@ -5202,7 +5208,7 @@
     </row>
     <row r="41" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>35</v>
@@ -5315,7 +5321,7 @@
     </row>
     <row r="42" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>40</v>
@@ -5403,7 +5409,7 @@
         <v>1.0096000000000001</v>
       </c>
       <c r="AI42" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AJ42" s="1">
         <f t="shared" si="8"/>
@@ -5429,7 +5435,7 @@
     </row>
     <row r="43" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>35</v>
@@ -5542,7 +5548,7 @@
     </row>
     <row r="44" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>35</v>
@@ -5629,7 +5635,7 @@
         <v>3.8</v>
       </c>
       <c r="AI44" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ44" s="1">
         <f t="shared" si="8"/>
@@ -5655,7 +5661,7 @@
     </row>
     <row r="45" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>40</v>
@@ -5740,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ45" s="1">
         <f t="shared" si="8"/>
@@ -5766,7 +5772,7 @@
     </row>
     <row r="46" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>35</v>
@@ -5853,7 +5859,7 @@
         <v>7.4</v>
       </c>
       <c r="AI46" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ46" s="1">
         <f t="shared" si="8"/>
@@ -5879,7 +5885,7 @@
     </row>
     <row r="47" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>40</v>
@@ -5968,7 +5974,7 @@
         <v>3.5659999999999998</v>
       </c>
       <c r="AI47" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ47" s="1">
         <f t="shared" si="8"/>
@@ -30826,7 +30832,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>24</v>
@@ -30834,7 +30840,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4">
         <v>64</v>
@@ -30842,7 +30848,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -30850,7 +30856,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>210</v>
@@ -30858,7 +30864,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>250</v>
@@ -30866,7 +30872,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8">
         <v>12</v>
@@ -30874,7 +30880,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -30882,7 +30888,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B10">
         <v>168</v>
@@ -30890,7 +30896,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>64</v>
@@ -30898,7 +30904,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B12">
         <v>12</v>
@@ -30916,7 +30922,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1">
         <v>200</v>
